--- a/r4-core-129-sample-organizations/StructureDefinition-at-core-ext-patient-religion.xlsx
+++ b/r4-core-129-sample-organizations/StructureDefinition-at-core-ext-patient-religion.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-11T21:26:51+00:00</t>
+    <t>2026-10-13T04:51:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-129-sample-organizations/StructureDefinition-at-core-ext-patient-religion.xlsx
+++ b/r4-core-129-sample-organizations/StructureDefinition-at-core-ext-patient-religion.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T04:51:46+00:00</t>
+    <t>2026-10-13T11:00:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-129-sample-organizations/StructureDefinition-at-core-ext-patient-religion.xlsx
+++ b/r4-core-129-sample-organizations/StructureDefinition-at-core-ext-patient-religion.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T11:00:34+00:00</t>
+    <t>2026-10-19T14:20:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-129-sample-organizations/StructureDefinition-at-core-ext-patient-religion.xlsx
+++ b/r4-core-129-sample-organizations/StructureDefinition-at-core-ext-patient-religion.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T14:20:01+00:00</t>
+    <t>2026-10-20T06:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
